--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -135,10 +135,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1886,10 +1886,8 @@
       <c r="I41" s="4" t="n">
         <v>1.67</v>
       </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J41" s="4" t="n">
+        <v>0.616</v>
       </c>
     </row>
     <row r="42">
@@ -1918,10 +1916,8 @@
       <c r="I42" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J42" s="6" t="n">
+        <v>0.604</v>
       </c>
     </row>
     <row r="43">
@@ -1950,10 +1946,8 @@
       <c r="I43" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J43" s="8" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="44">
@@ -1990,10 +1984,8 @@
       <c r="I44" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J44" s="4" t="n">
+        <v>0.616</v>
       </c>
     </row>
     <row r="45">
@@ -2022,10 +2014,8 @@
       <c r="I45" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J45" s="6" t="n">
+        <v>0.604</v>
       </c>
     </row>
     <row r="46">
@@ -2054,10 +2044,8 @@
       <c r="I46" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J46" s="8" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="47">
@@ -2094,10 +2082,8 @@
       <c r="I47" s="4" t="n">
         <v>3.67</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J47" s="4" t="n">
+        <v>0.616</v>
       </c>
     </row>
     <row r="48">
@@ -2126,10 +2112,8 @@
       <c r="I48" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J48" s="6" t="n">
+        <v>0.604</v>
       </c>
     </row>
     <row r="49">
@@ -2158,10 +2142,8 @@
       <c r="I49" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J49" s="8" t="n">
+        <v>0.628</v>
       </c>
     </row>
     <row r="50">
@@ -2198,10 +2180,8 @@
       <c r="I50" s="4" t="n">
         <v>2.07</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J50" s="4" t="n">
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2230,10 +2210,8 @@
       <c r="I51" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J51" s="6" t="n">
+        <v>0.768</v>
       </c>
     </row>
     <row r="52">
@@ -2262,10 +2240,8 @@
       <c r="I52" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J52" s="8" t="n">
+        <v>0.805</v>
       </c>
     </row>
     <row r="53">
@@ -2302,10 +2278,8 @@
       <c r="I53" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J53" s="4" t="n">
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2334,10 +2308,8 @@
       <c r="I54" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J54" s="6" t="n">
+        <v>0.768</v>
       </c>
     </row>
     <row r="55">
@@ -2366,10 +2338,8 @@
       <c r="I55" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J55" s="8" t="n">
+        <v>0.805</v>
       </c>
     </row>
     <row r="56">
@@ -2406,10 +2376,8 @@
       <c r="I56" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J56" s="4" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="57">
@@ -2438,10 +2406,8 @@
       <c r="I57" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J57" s="6" t="n">
+        <v>0.829</v>
       </c>
     </row>
     <row r="58">
@@ -2470,10 +2436,8 @@
       <c r="I58" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J58" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J58" s="8" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="59">
@@ -2510,10 +2474,8 @@
       <c r="I59" s="4" t="n">
         <v>1.6</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J59" s="4" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="60">
@@ -2542,10 +2504,8 @@
       <c r="I60" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J60" s="6" t="n">
+        <v>0.829</v>
       </c>
     </row>
     <row r="61">
@@ -2574,10 +2534,8 @@
       <c r="I61" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J61" s="8" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="62">
@@ -2614,10 +2572,8 @@
       <c r="I62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J62" s="4" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="63">
@@ -2646,10 +2602,8 @@
       <c r="I63" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J63" s="6" t="n">
+        <v>0.829</v>
       </c>
     </row>
     <row r="64">
@@ -2678,10 +2632,8 @@
       <c r="I64" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J64" s="8" t="n">
+        <v>0.835</v>
       </c>
     </row>
     <row r="65">
@@ -2718,10 +2670,8 @@
       <c r="I65" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="4" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="66">
@@ -2750,10 +2700,8 @@
       <c r="I66" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J66" s="6" t="n">
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2782,10 +2730,8 @@
       <c r="I67" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J67" s="8" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="68">
@@ -2822,10 +2768,8 @@
       <c r="I68" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J68" s="4" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="69">
@@ -2854,10 +2798,8 @@
       <c r="I69" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J69" s="6" t="n">
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2886,10 +2828,8 @@
       <c r="I70" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="8" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="71">
@@ -2926,10 +2866,8 @@
       <c r="I71" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J71" s="4" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="72">
@@ -2958,10 +2896,8 @@
       <c r="I72" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="6" t="n">
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="73">
@@ -2990,10 +2926,8 @@
       <c r="I73" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="8" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="74">
@@ -3030,10 +2964,8 @@
       <c r="I74" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="4" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="75">
@@ -3062,10 +2994,8 @@
       <c r="I75" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J75" s="6" t="n">
+        <v>0.9330000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3094,10 +3024,8 @@
       <c r="I76" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J76" s="8" t="n">
+        <v>0.896</v>
       </c>
     </row>
     <row r="77">
@@ -3500,7 +3428,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3512,7 +3440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3520,6 +3448,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3555,6 +3484,11 @@
           <t>Best Pipeline</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
@@ -3565,15 +3499,20 @@
       <c r="B3" s="11" t="n">
         <v>0.842</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="12" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="12" t="n">
         <v>0.835</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="11" t="inlineStr">
         <is>
           <t>iterative</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>+0.7%</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3522,7 @@
           <t>gemma3:27b</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.878</v>
       </c>
       <c r="C4" s="14" t="n">
@@ -3592,9 +3531,14 @@
       <c r="D4" s="14" t="n">
         <v>0.86</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="11" t="inlineStr">
         <is>
           <t>iterative</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>+1.8%</t>
         </is>
       </c>
     </row>
@@ -3604,45 +3548,159 @@
           <t>gpt-oss:20b</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="12" t="n">
         <v>0.945</v>
       </c>
       <c r="C5" s="11" t="n">
         <v>0.951</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="12" t="n">
         <v>0.9330000000000001</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>batch</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>+0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>+0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>+2.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
           <t>qwen3:8b</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B10" s="11" t="n">
         <v>0.884</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C10" s="14" t="n">
         <v>0.872</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D10" s="14" t="n">
         <v>0.842</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>iterative</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>+1.2%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3659,15 +3717,15 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Iterative vs Batch vs NoTDD — pass@1 per Model &amp; Preset</t>
+          <t>Iterative vs Batch vs NoTDD — pass@1</t>
         </is>
       </c>
     </row>
@@ -3684,17 +3742,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Iterative pass@1</t>
+          <t>Iterative</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Batch pass@1</t>
+          <t>Batch</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>NoTDD pass@1</t>
+          <t>NoTDD</t>
         </is>
       </c>
     </row>
@@ -3709,13 +3767,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="11" t="n">
+      <c r="C3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="12" t="n">
         <v>0.9333</v>
       </c>
     </row>
@@ -3730,13 +3788,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D4" s="14" t="n">
         <v>0.8667</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3751,13 +3809,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="n">
+      <c r="C5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3772,7 +3830,7 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="n">
@@ -3793,13 +3851,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="12" t="n">
+      <c r="C7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3814,13 +3872,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="12" t="n">
+      <c r="C8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3835,13 +3893,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="C9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3856,13 +3914,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="12" t="n">
+      <c r="C10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3877,13 +3935,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12" t="n">
+      <c r="C11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3898,13 +3956,13 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="14" t="n">
         <v>0.9</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3919,13 +3977,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="C13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>0.95</v>
       </c>
     </row>
@@ -3940,13 +3998,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12" t="n">
+      <c r="C14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3961,13 +4019,13 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11" t="n">
+      <c r="C15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.9</v>
       </c>
     </row>
@@ -3985,7 +4043,7 @@
       <c r="C16" s="14" t="n">
         <v>0.8667</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="11" t="n">
         <v>0.9333</v>
       </c>
       <c r="E16" s="14" t="n">
@@ -4003,13 +4061,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="12" t="n">
         <v>0.9</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="11" t="n">
         <v>0.95</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="12" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -4024,13 +4082,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="11" t="n">
         <v>0.3333</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="11" t="n">
         <v>0.3333</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>0.3333</v>
       </c>
     </row>
@@ -4045,13 +4103,13 @@
           <t>easy</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="12" t="n">
         <v>0.7333</v>
       </c>
-      <c r="D19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="n">
+      <c r="D19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="12" t="n">
         <v>0.7333</v>
       </c>
     </row>
@@ -4066,13 +4124,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="11" t="n">
         <v>0.8667</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>0.7333</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="11" t="n">
         <v>0.8667</v>
       </c>
     </row>
@@ -4087,13 +4145,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="12" t="n">
         <v>0.8</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="11" t="n">
         <v>0.9333</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="12" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -4111,7 +4169,7 @@
       <c r="C22" s="14" t="n">
         <v>0.85</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="11" t="n">
         <v>0.95</v>
       </c>
       <c r="E22" s="14" t="n">
@@ -4129,13 +4187,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="n">
+      <c r="C23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4150,13 +4208,13 @@
           <t>easy</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="12" t="n">
+      <c r="C24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4171,13 +4229,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12" t="n">
+      <c r="C25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4192,13 +4250,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12" t="n">
+      <c r="C26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4213,13 +4271,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="12" t="n">
+      <c r="C27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4234,13 +4292,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="n">
+      <c r="C28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4255,13 +4313,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12" t="n">
+      <c r="C29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4276,13 +4334,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12" t="n">
+      <c r="C30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4297,13 +4355,13 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="C31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4334,7 +4392,7 @@
     <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Mutation Score — Iterative vs Batch vs NoTDD</t>
+          <t>Mutation Score — Code Quality Comparison</t>
         </is>
       </c>
     </row>
@@ -4376,13 +4434,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="12" t="n">
+      <c r="C3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4397,13 +4455,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="12" t="n">
+      <c r="C4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4418,13 +4476,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="12" t="n">
+      <c r="C5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4439,13 +4497,13 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4460,13 +4518,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>0.921</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>0.945</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="12" t="n">
         <v>0.9330000000000001</v>
       </c>
     </row>
@@ -4481,10 +4539,10 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="11" t="n">
         <v>0.958</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>0.958</v>
       </c>
       <c r="E8" s="14" t="n">
@@ -4502,13 +4560,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11" t="n">
+      <c r="C9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>0.983</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4523,10 +4581,10 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <v>0.958</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>0.958</v>
       </c>
       <c r="E10" s="14" t="n">
@@ -4544,13 +4602,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="12" t="n">
+      <c r="C11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4568,7 +4626,7 @@
       <c r="C12" s="14" t="n">
         <v>0.757</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="11" t="n">
         <v>0.836</v>
       </c>
       <c r="E12" s="14" t="n">
@@ -4586,13 +4644,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.873</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="11" t="n">
         <v>0.949</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.897</v>
       </c>
     </row>
@@ -4613,7 +4671,7 @@
       <c r="D14" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="E14" s="11" t="n">
         <v>0.955</v>
       </c>
     </row>
@@ -4628,13 +4686,13 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>0.793</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="11" t="n">
         <v>0.962</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>0.82</v>
       </c>
     </row>
@@ -4649,13 +4707,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12" t="n">
+      <c r="C16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4670,13 +4728,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4691,13 +4749,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="11" t="n">
         <v>0.3333</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="11" t="n">
         <v>0.3333</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>0.3333</v>
       </c>
     </row>
@@ -4712,13 +4770,13 @@
           <t>easy</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="12" t="n">
+      <c r="C19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4733,13 +4791,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12" t="n">
+      <c r="C20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4754,13 +4812,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="n">
+      <c r="C21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4775,13 +4833,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="12" t="n">
+      <c r="C22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4796,13 +4854,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="12" t="n">
+      <c r="C23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4817,13 +4875,13 @@
           <t>easy</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="12" t="n">
+      <c r="C24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4838,13 +4896,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="12" t="n">
+      <c r="C25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4859,13 +4917,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12" t="n">
+      <c r="C26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4880,13 +4938,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="12" t="n">
+      <c r="C27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4901,13 +4959,13 @@
           <t>medium</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="n">
+      <c r="C28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4922,13 +4980,13 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="12" t="n">
+      <c r="C29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4943,13 +5001,13 @@
           <t>very_hard</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12" t="n">
+      <c r="C30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4964,13 +5022,13 @@
           <t>extremely_hard</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="C31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>1</v>
       </c>
     </row>

--- a/benchmark_results.xlsx
+++ b/benchmark_results.xlsx
@@ -11,8 +11,11 @@
     <sheet name="HumanEval" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Pipeline Comparison" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Mutation Scores" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="JASP Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JASP Data'!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -9212,4 +9215,6158 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M136"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>model_size_b</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>preset</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>preset_difficulty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pipeline</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pass_at_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>pass_at_5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>mutation_score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>avg_loc</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>avg_cc</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>avg_attempts</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>humaneval_pass1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>is_estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="17" t="n"/>
+      <c r="J2" s="17" t="n"/>
+      <c r="K2" s="17" t="n"/>
+      <c r="L2" s="17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M2" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="17" t="n"/>
+      <c r="J3" s="17" t="n"/>
+      <c r="K3" s="17" t="n"/>
+      <c r="L3" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M3" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
+      <c r="K4" s="17" t="n"/>
+      <c r="L4" s="17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M4" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="J5" s="17" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="K5" s="17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M5" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="J6" s="17" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="K6" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M6" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J7" s="17" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="K7" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M7" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="K8" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M16" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="17" t="n"/>
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M17" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="17" t="n"/>
+      <c r="L18" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="17" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M27" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+      <c r="L30" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:12b</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M31" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
+      <c r="L32" s="17" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="M32" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="M33" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M34" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="17" t="n"/>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="17" t="n"/>
+      <c r="L35" s="17" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17" t="n"/>
+      <c r="L36" s="17" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="M36" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K39" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="M39" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="M41" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K42" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M43" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="K44" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="M44" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="M45" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="17" t="inlineStr">
+        <is>
+          <t>gemma3:27b</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K46" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M46" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="17" t="n"/>
+      <c r="K47" s="17" t="n"/>
+      <c r="L47" s="17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M47" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" s="17" t="n"/>
+      <c r="J48" s="17" t="n"/>
+      <c r="K48" s="17" t="n"/>
+      <c r="L48" s="17" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="M48" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M49" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+      <c r="L50" s="17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" s="17" t="n"/>
+      <c r="J51" s="17" t="n"/>
+      <c r="K51" s="17" t="n"/>
+      <c r="L51" s="17" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="M51" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="17" t="n"/>
+      <c r="J52" s="17" t="n"/>
+      <c r="K52" s="17" t="n"/>
+      <c r="L52" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K53" s="17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L53" s="17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M53" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K54" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="M54" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C55" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="J55" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="K55" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M55" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M56" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K57" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="17" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="M57" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K58" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="J59" s="17" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K59" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C60" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="J60" s="17" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K60" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="17" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="M60" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>gpt-oss:20b</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F61" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" s="17" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="I61" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="J61" s="17" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="K61" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M61" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C62" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="17" t="n"/>
+      <c r="J62" s="17" t="n"/>
+      <c r="K62" s="17" t="n"/>
+      <c r="L62" s="17" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="M62" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="17" t="n"/>
+      <c r="J63" s="17" t="n"/>
+      <c r="K63" s="17" t="n"/>
+      <c r="L63" s="17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="M63" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="17" t="n"/>
+      <c r="J64" s="17" t="n"/>
+      <c r="K64" s="17" t="n"/>
+      <c r="L64" s="17" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M64" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="G65" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="17" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J65" s="17" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="K65" s="17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L65" s="17" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="M65" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="G66" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I66" s="17" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J66" s="17" t="n">
+        <v>8.869999999999999</v>
+      </c>
+      <c r="K66" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="M66" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="G67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="17" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J67" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K67" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="17" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M67" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G68" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="17" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J68" s="17" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K68" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L68" s="17" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="M68" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G69" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="17" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J69" s="17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K69" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" s="17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="M69" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="17" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="J70" s="17" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="K70" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="17" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M70" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G71" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H71" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I71" s="17" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="J71" s="17" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="K71" s="17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="L71" s="17" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="M71" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B72" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G72" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H72" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I72" s="17" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="J72" s="17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K72" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="M72" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G73" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H73" s="17" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="I73" s="17" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="J73" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K73" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" s="17" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M73" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="17" t="n"/>
+      <c r="J74" s="17" t="n"/>
+      <c r="K74" s="17" t="n"/>
+      <c r="L74" s="17" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="M74" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B75" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="17" t="n"/>
+      <c r="J75" s="17" t="n"/>
+      <c r="K75" s="17" t="n"/>
+      <c r="L75" s="17" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="M75" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>llama3.1:8b</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="17" t="n"/>
+      <c r="J76" s="17" t="n"/>
+      <c r="K76" s="17" t="n"/>
+      <c r="L76" s="17" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="M76" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B77" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="G77" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J77" s="17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K77" s="17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="L77" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M77" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="J78" s="17" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="K78" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="17" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="M78" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="G79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="17" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J79" s="17" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K79" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="17" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M79" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="G80" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" s="17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J80" s="17" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K80" s="17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L80" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M80" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D81" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="G81" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="17" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J81" s="17" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="K81" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="17" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="M81" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D82" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="n">
+        <v>0.8667</v>
+      </c>
+      <c r="G82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="J82" s="17" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K82" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="17" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M82" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C83" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D83" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="17" t="n"/>
+      <c r="J83" s="17" t="n"/>
+      <c r="K83" s="17" t="n"/>
+      <c r="L83" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M83" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D84" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="17" t="n"/>
+      <c r="J84" s="17" t="n"/>
+      <c r="K84" s="17" t="n"/>
+      <c r="L84" s="17" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="M84" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C85" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D85" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="17" t="n"/>
+      <c r="J85" s="17" t="n"/>
+      <c r="K85" s="17" t="n"/>
+      <c r="L85" s="17" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M85" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C86" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D86" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E86" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="17" t="n"/>
+      <c r="J86" s="17" t="n"/>
+      <c r="K86" s="17" t="n"/>
+      <c r="L86" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M86" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D87" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="17" t="n"/>
+      <c r="J87" s="17" t="n"/>
+      <c r="K87" s="17" t="n"/>
+      <c r="L87" s="17" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="M87" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C88" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D88" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="17" t="n"/>
+      <c r="J88" s="17" t="n"/>
+      <c r="K88" s="17" t="n"/>
+      <c r="L88" s="17" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M88" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B89" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C89" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D89" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E89" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="17" t="n"/>
+      <c r="J89" s="17" t="n"/>
+      <c r="K89" s="17" t="n"/>
+      <c r="L89" s="17" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="M89" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B90" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D90" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="17" t="n"/>
+      <c r="J90" s="17" t="n"/>
+      <c r="K90" s="17" t="n"/>
+      <c r="L90" s="17" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="M90" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:3b</t>
+        </is>
+      </c>
+      <c r="B91" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C91" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D91" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F91" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="17" t="n"/>
+      <c r="J91" s="17" t="n"/>
+      <c r="K91" s="17" t="n"/>
+      <c r="L91" s="17" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M91" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B92" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C92" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D92" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="17" t="n"/>
+      <c r="J92" s="17" t="n"/>
+      <c r="K92" s="17" t="n"/>
+      <c r="L92" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M92" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B93" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C93" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D93" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" s="17" t="n"/>
+      <c r="J93" s="17" t="n"/>
+      <c r="K93" s="17" t="n"/>
+      <c r="L93" s="17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M93" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B94" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C94" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="17" t="n"/>
+      <c r="J94" s="17" t="n"/>
+      <c r="K94" s="17" t="n"/>
+      <c r="L94" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M94" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B95" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C95" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D95" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G95" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="17" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J95" s="17" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K95" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L95" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M95" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B96" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D96" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="n">
+        <v>0.9333</v>
+      </c>
+      <c r="G96" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="J96" s="17" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="K96" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M96" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B97" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C97" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="17" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J97" s="17" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K97" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M97" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B98" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C98" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D98" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="17" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J98" s="17" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K98" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L98" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M98" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B99" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C99" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D99" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G99" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="J99" s="17" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="K99" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M99" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B100" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C100" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D100" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G100" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="17" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J100" s="17" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="K100" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M100" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B101" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C101" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D101" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="17" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J101" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K101" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M101" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B102" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D102" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="17" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="J102" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K102" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M102" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B103" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D103" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="17" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="J103" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K103" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M103" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C104" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D104" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="17" t="n"/>
+      <c r="J104" s="17" t="n"/>
+      <c r="K104" s="17" t="n"/>
+      <c r="L104" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M104" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B105" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C105" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D105" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="17" t="n"/>
+      <c r="J105" s="17" t="n"/>
+      <c r="K105" s="17" t="n"/>
+      <c r="L105" s="17" t="n">
+        <v>0.829</v>
+      </c>
+      <c r="M105" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="17" t="inlineStr">
+        <is>
+          <t>qwen2.5-coder:7b</t>
+        </is>
+      </c>
+      <c r="B106" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C106" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D106" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="17" t="n"/>
+      <c r="J106" s="17" t="n"/>
+      <c r="K106" s="17" t="n"/>
+      <c r="L106" s="17" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="M106" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B107" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C107" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="17" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J107" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K107" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L107" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M107" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B108" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="17" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J108" s="17" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="K108" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M108" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B109" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="17" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J109" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K109" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" s="17" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M109" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B110" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D110" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J110" s="17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K110" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M110" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B111" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C111" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D111" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="J111" s="17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="K111" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M111" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C112" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D112" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="J112" s="17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K112" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="17" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M112" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="17" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J113" s="17" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="K113" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M113" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B114" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C114" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="17" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J114" s="17" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="K114" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M114" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B115" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C115" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="17" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J115" s="17" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="K115" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="17" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M115" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D116" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="17" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J116" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K116" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M116" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C117" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D117" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="17" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J117" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K117" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M117" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B118" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C118" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D118" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="17" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J118" s="17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K118" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="17" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M118" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C119" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D119" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="17" t="n"/>
+      <c r="J119" s="17" t="n"/>
+      <c r="K119" s="17" t="n"/>
+      <c r="L119" s="17" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="M119" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B120" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D120" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="17" t="n"/>
+      <c r="J120" s="17" t="n"/>
+      <c r="K120" s="17" t="n"/>
+      <c r="L120" s="17" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="M120" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:4b</t>
+        </is>
+      </c>
+      <c r="B121" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C121" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D121" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="17" t="n"/>
+      <c r="J121" s="17" t="n"/>
+      <c r="K121" s="17" t="n"/>
+      <c r="L121" s="17" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M121" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B122" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C122" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="17" t="n"/>
+      <c r="J122" s="17" t="n"/>
+      <c r="K122" s="17" t="n"/>
+      <c r="L122" s="17" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="M122" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C123" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="17" t="n"/>
+      <c r="J123" s="17" t="n"/>
+      <c r="K123" s="17" t="n"/>
+      <c r="L123" s="17" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="M123" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B124" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="D124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I124" s="17" t="n"/>
+      <c r="J124" s="17" t="n"/>
+      <c r="K124" s="17" t="n"/>
+      <c r="L124" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M124" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D125" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="17" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J125" s="17" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="K125" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="17" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="M125" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B126" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D126" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E126" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="17" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J126" s="17" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="K126" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="17" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="M126" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C127" s="17" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="D127" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="17" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="J127" s="17" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="K127" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M127" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B128" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C128" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D128" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="17" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J128" s="17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K128" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" s="17" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="M128" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C129" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D129" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I129" s="17" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="J129" s="17" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="K129" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" s="17" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="M129" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B130" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C130" s="17" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="D130" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="17" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="J130" s="17" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="K130" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M130" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B131" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C131" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D131" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E131" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J131" s="17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K131" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" s="17" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="M131" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B132" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C132" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D132" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E132" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="17" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="J132" s="17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K132" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" s="17" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="M132" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B133" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C133" s="17" t="inlineStr">
+        <is>
+          <t>very_hard</t>
+        </is>
+      </c>
+      <c r="D133" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="J133" s="17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K133" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M133" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B134" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C134" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D134" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>iterative</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I134" s="17" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J134" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K134" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" s="17" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="M134" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B135" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C135" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D135" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I135" s="17" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="J135" s="17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K135" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="17" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="M135" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="inlineStr">
+        <is>
+          <t>qwen3:8b</t>
+        </is>
+      </c>
+      <c r="B136" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="C136" s="17" t="inlineStr">
+        <is>
+          <t>extremely_hard</t>
+        </is>
+      </c>
+      <c r="D136" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>notdd</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I136" s="17" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J136" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K136" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" s="17" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="M136" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>